--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2017/American_Aircraft_Cumulative_Statistics_2017.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2017/American_Aircraft_Cumulative_Statistics_2017.xlsx
@@ -13,33 +13,51 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="27" uniqueCount="27">
   <si>
     <t>Row</t>
   </si>
   <si>
-    <t>Allegiant</t>
-  </si>
-  <si>
-    <t>American</t>
-  </si>
-  <si>
-    <t>Delta</t>
-  </si>
-  <si>
-    <t>Frontier</t>
-  </si>
-  <si>
-    <t>JetBlue</t>
-  </si>
-  <si>
-    <t>Spirit</t>
-  </si>
-  <si>
-    <t>United</t>
-  </si>
-  <si>
-    <t>All Airlines</t>
+    <t>E190</t>
+  </si>
+  <si>
+    <t>A319</t>
+  </si>
+  <si>
+    <t>A320</t>
+  </si>
+  <si>
+    <t>A321</t>
+  </si>
+  <si>
+    <t>B737-800</t>
+  </si>
+  <si>
+    <t>B757-200</t>
+  </si>
+  <si>
+    <t>B767-300</t>
+  </si>
+  <si>
+    <t>A330-200</t>
+  </si>
+  <si>
+    <t>A330-300</t>
+  </si>
+  <si>
+    <t>B787-8</t>
+  </si>
+  <si>
+    <t>B787-9</t>
+  </si>
+  <si>
+    <t>B777-200</t>
+  </si>
+  <si>
+    <t>B777-300</t>
+  </si>
+  <si>
+    <t>All Aircraft</t>
   </si>
   <si>
     <t>RPMs</t>
@@ -121,10 +139,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" customWidth="true"/>
+    <col min="1" max="1" width="9.140625" customWidth="true"/>
     <col min="2" max="2" width="15.85546875" customWidth="true"/>
     <col min="3" max="3" width="15.85546875" customWidth="true"/>
     <col min="4" max="4" width="13.140625" customWidth="true"/>
@@ -144,40 +162,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
@@ -185,40 +203,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>3624402512</v>
+        <v>1203688674</v>
       </c>
       <c r="C2" s="0">
-        <v>4448318805</v>
+        <v>1520261681</v>
       </c>
       <c r="D2" s="0">
-        <v>523332</v>
+        <v>208255</v>
       </c>
       <c r="E2" s="0">
-        <v>179</v>
+        <v>99</v>
       </c>
       <c r="F2" s="0">
-        <v>28132</v>
+        <v>32112</v>
       </c>
       <c r="G2" s="0">
-        <v>3.3100000000000001</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="H2" s="0">
-        <v>7.6200000000000001</v>
+        <v>7.8099999999999996</v>
       </c>
       <c r="I2" s="0">
-        <v>81.480000000000004</v>
+        <v>79.180000000000007</v>
       </c>
       <c r="J2" s="0">
-        <v>882</v>
+        <v>478</v>
       </c>
       <c r="K2" s="0">
-        <v>3503</v>
+        <v>2174.8200000000002</v>
       </c>
       <c r="L2" s="0">
-        <v>19.530000000000001</v>
+        <v>21.969999999999999</v>
       </c>
       <c r="M2" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.082000000000000003</v>
       </c>
     </row>
     <row r="3">
@@ -226,40 +244,40 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>6988399308</v>
+        <v>14678360503</v>
       </c>
       <c r="C3" s="0">
-        <v>8355507712</v>
+        <v>18137072137</v>
       </c>
       <c r="D3" s="0">
-        <v>467834</v>
+        <v>397830</v>
       </c>
       <c r="E3" s="0">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="F3" s="0">
-        <v>65156</v>
+        <v>179958</v>
       </c>
       <c r="G3" s="0">
-        <v>3.6499999999999999</v>
+        <v>3.9500000000000002</v>
       </c>
       <c r="H3" s="0">
-        <v>8.8599999999999994</v>
+        <v>9</v>
       </c>
       <c r="I3" s="0">
-        <v>83.640000000000001</v>
+        <v>80.930000000000007</v>
       </c>
       <c r="J3" s="0">
-        <v>855</v>
+        <v>787</v>
       </c>
       <c r="K3" s="0">
-        <v>3625</v>
+        <v>3174.1300000000001</v>
       </c>
       <c r="L3" s="0">
-        <v>24.170000000000002</v>
+        <v>24.800000000000001</v>
       </c>
       <c r="M3" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.071999999999999995</v>
       </c>
     </row>
     <row r="4">
@@ -267,40 +285,40 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>10966663621</v>
+        <v>6988399308</v>
       </c>
       <c r="C4" s="0">
-        <v>12872989409</v>
+        <v>8355507712</v>
       </c>
       <c r="D4" s="0">
-        <v>542477</v>
+        <v>467834</v>
       </c>
       <c r="E4" s="0">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="F4" s="0">
-        <v>87529</v>
+        <v>65156</v>
       </c>
       <c r="G4" s="0">
-        <v>3.6899999999999999</v>
+        <v>3.6499999999999999</v>
       </c>
       <c r="H4" s="0">
-        <v>9.3100000000000005</v>
+        <v>8.8599999999999994</v>
       </c>
       <c r="I4" s="0">
-        <v>85.189999999999998</v>
+        <v>83.640000000000001</v>
       </c>
       <c r="J4" s="0">
-        <v>928</v>
+        <v>855</v>
       </c>
       <c r="K4" s="0">
-        <v>4025</v>
+        <v>3625.2199999999998</v>
       </c>
       <c r="L4" s="0">
-        <v>25.399999999999999</v>
+        <v>24.170000000000002</v>
       </c>
       <c r="M4" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.069000000000000006</v>
       </c>
     </row>
     <row r="5">
@@ -308,40 +326,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>9320751561</v>
+        <v>50623270060</v>
       </c>
       <c r="C5" s="0">
-        <v>10736046000</v>
+        <v>59134179059</v>
       </c>
       <c r="D5" s="0">
-        <v>1110243</v>
+        <v>759786</v>
       </c>
       <c r="E5" s="0">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F5" s="0">
-        <v>50652</v>
+        <v>259202</v>
       </c>
       <c r="G5" s="0">
-        <v>5.2400000000000002</v>
+        <v>3.3300000000000001</v>
       </c>
       <c r="H5" s="0">
-        <v>15.800000000000001</v>
+        <v>10.970000000000001</v>
       </c>
       <c r="I5" s="0">
-        <v>86.819999999999993</v>
+        <v>85.609999999999999</v>
       </c>
       <c r="J5" s="0">
-        <v>1178</v>
+        <v>1285</v>
       </c>
       <c r="K5" s="0">
-        <v>2677</v>
+        <v>4549.04</v>
       </c>
       <c r="L5" s="0">
-        <v>14.869999999999999</v>
+        <v>25.559999999999999</v>
       </c>
       <c r="M5" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.066000000000000003</v>
       </c>
     </row>
     <row r="6">
@@ -349,40 +367,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>28558156106</v>
+        <v>53366123071</v>
       </c>
       <c r="C6" s="0">
-        <v>33898833300</v>
+        <v>63095062997</v>
       </c>
       <c r="D6" s="0">
-        <v>714111</v>
+        <v>586549</v>
       </c>
       <c r="E6" s="0">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="F6" s="0">
-        <v>187946</v>
+        <v>363335</v>
       </c>
       <c r="G6" s="0">
-        <v>3.96</v>
+        <v>3.3799999999999999</v>
       </c>
       <c r="H6" s="0">
-        <v>12.15</v>
+        <v>9.8200000000000003</v>
       </c>
       <c r="I6" s="0">
-        <v>84.25</v>
+        <v>84.579999999999998</v>
       </c>
       <c r="J6" s="0">
-        <v>1202</v>
+        <v>1085</v>
       </c>
       <c r="K6" s="0">
-        <v>3689</v>
+        <v>3921.9299999999998</v>
       </c>
       <c r="L6" s="0">
-        <v>24.600000000000001</v>
+        <v>24.510000000000002</v>
       </c>
       <c r="M6" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.066000000000000003</v>
       </c>
     </row>
     <row r="7">
@@ -390,40 +408,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>12433997975</v>
+        <v>9060024983</v>
       </c>
       <c r="C7" s="0">
-        <v>15047556180</v>
+        <v>10929360585</v>
       </c>
       <c r="D7" s="0">
-        <v>792394</v>
+        <v>658792</v>
       </c>
       <c r="E7" s="0">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F7" s="0">
-        <v>85976</v>
+        <v>34827</v>
       </c>
       <c r="G7" s="0">
-        <v>4.5300000000000002</v>
+        <v>2.1000000000000001</v>
       </c>
       <c r="H7" s="0">
-        <v>11.66</v>
+        <v>8.8399999999999999</v>
       </c>
       <c r="I7" s="0">
-        <v>82.629999999999995</v>
+        <v>82.900000000000006</v>
       </c>
       <c r="J7" s="0">
-        <v>972</v>
+        <v>1769</v>
       </c>
       <c r="K7" s="0">
-        <v>3112</v>
+        <v>5132.5600000000004</v>
       </c>
       <c r="L7" s="0">
-        <v>17.289999999999999</v>
+        <v>28.920000000000002</v>
       </c>
       <c r="M7" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.069000000000000006</v>
       </c>
     </row>
     <row r="8">
@@ -431,40 +449,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>15797905721</v>
+        <v>7192997792</v>
       </c>
       <c r="C8" s="0">
-        <v>18406088100</v>
+        <v>8939910957</v>
       </c>
       <c r="D8" s="0">
-        <v>517607</v>
+        <v>849801</v>
       </c>
       <c r="E8" s="0">
-        <v>150</v>
+        <v>208</v>
       </c>
       <c r="F8" s="0">
-        <v>122489</v>
+        <v>16596</v>
       </c>
       <c r="G8" s="0">
-        <v>3.4399999999999999</v>
+        <v>1.5800000000000001</v>
       </c>
       <c r="H8" s="0">
-        <v>9.1999999999999993</v>
+        <v>9.1600000000000001</v>
       </c>
       <c r="I8" s="0">
-        <v>85.829999999999998</v>
+        <v>80.459999999999994</v>
       </c>
       <c r="J8" s="0">
-        <v>1002</v>
+        <v>2610</v>
       </c>
       <c r="K8" s="0">
-        <v>4212</v>
+        <v>6555.1999999999998</v>
       </c>
       <c r="L8" s="0">
-        <v>28.079999999999998</v>
+        <v>31.73</v>
       </c>
       <c r="M8" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.070999999999999994</v>
       </c>
     </row>
     <row r="9">
@@ -472,40 +490,286 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>87690276804</v>
+        <v>5471021523</v>
       </c>
       <c r="C9" s="0">
-        <v>103765339506</v>
+        <v>7256312304</v>
       </c>
       <c r="D9" s="0">
-        <v>641398</v>
+        <v>1324145</v>
       </c>
       <c r="E9" s="0">
-        <v>159</v>
+        <v>254</v>
       </c>
       <c r="F9" s="0">
-        <v>627880</v>
+        <v>9484</v>
       </c>
       <c r="G9" s="0">
-        <v>3.8799999999999999</v>
+        <v>1.73</v>
       </c>
       <c r="H9" s="0">
-        <v>10.640000000000001</v>
+        <v>11.4</v>
       </c>
       <c r="I9" s="0">
-        <v>84.510000000000005</v>
+        <v>75.400000000000006</v>
       </c>
       <c r="J9" s="0">
-        <v>1041</v>
+        <v>3023</v>
       </c>
       <c r="K9" s="0">
-        <v>3655</v>
+        <v>7896.4399999999996</v>
       </c>
       <c r="L9" s="0">
-        <v>23.030000000000001</v>
+        <v>31.18</v>
       </c>
       <c r="M9" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.068000000000000005</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="0">
+        <v>3996096859</v>
+      </c>
+      <c r="C10" s="0">
+        <v>5226442202</v>
+      </c>
+      <c r="D10" s="0">
+        <v>1578986</v>
+      </c>
+      <c r="E10" s="0">
+        <v>287</v>
+      </c>
+      <c r="F10" s="0">
+        <v>4980</v>
+      </c>
+      <c r="G10" s="0">
+        <v>1.5</v>
+      </c>
+      <c r="H10" s="0">
+        <v>11.800000000000001</v>
+      </c>
+      <c r="I10" s="0">
+        <v>76.459999999999994</v>
+      </c>
+      <c r="J10" s="0">
+        <v>3666</v>
+      </c>
+      <c r="K10" s="0">
+        <v>8928.0499999999993</v>
+      </c>
+      <c r="L10" s="0">
+        <v>31.18</v>
+      </c>
+      <c r="M10" s="0">
+        <v>0.067000000000000004</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="0">
+        <v>8255970223</v>
+      </c>
+      <c r="C11" s="0">
+        <v>10287204656</v>
+      </c>
+      <c r="D11" s="0">
+        <v>1442806</v>
+      </c>
+      <c r="E11" s="0">
+        <v>225</v>
+      </c>
+      <c r="F11" s="0">
+        <v>8781</v>
+      </c>
+      <c r="G11" s="0">
+        <v>1.23</v>
+      </c>
+      <c r="H11" s="0">
+        <v>12.77</v>
+      </c>
+      <c r="I11" s="0">
+        <v>80.25</v>
+      </c>
+      <c r="J11" s="0">
+        <v>5199</v>
+      </c>
+      <c r="K11" s="0">
+        <v>7595.1999999999998</v>
+      </c>
+      <c r="L11" s="0">
+        <v>33.700000000000003</v>
+      </c>
+      <c r="M11" s="0">
+        <v>0.067000000000000004</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="0">
+        <v>4526855886</v>
+      </c>
+      <c r="C12" s="0">
+        <v>5685266489</v>
+      </c>
+      <c r="D12" s="0">
+        <v>1722808</v>
+      </c>
+      <c r="E12" s="0">
+        <v>285</v>
+      </c>
+      <c r="F12" s="0">
+        <v>3891</v>
+      </c>
+      <c r="G12" s="0">
+        <v>1.1799999999999999</v>
+      </c>
+      <c r="H12" s="0">
+        <v>11.970000000000001</v>
+      </c>
+      <c r="I12" s="0">
+        <v>79.620000000000005</v>
+      </c>
+      <c r="J12" s="0">
+        <v>5134</v>
+      </c>
+      <c r="K12" s="0">
+        <v>9336.4799999999996</v>
+      </c>
+      <c r="L12" s="0">
+        <v>32.810000000000002</v>
+      </c>
+      <c r="M12" s="0">
+        <v>0.065000000000000002</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="0">
+        <v>19000465037</v>
+      </c>
+      <c r="C13" s="0">
+        <v>23923931130</v>
+      </c>
+      <c r="D13" s="0">
+        <v>1394168</v>
+      </c>
+      <c r="E13" s="0">
+        <v>272</v>
+      </c>
+      <c r="F13" s="0">
+        <v>20162</v>
+      </c>
+      <c r="G13" s="0">
+        <v>1.1699999999999999</v>
+      </c>
+      <c r="H13" s="0">
+        <v>10.41</v>
+      </c>
+      <c r="I13" s="0">
+        <v>79.420000000000002</v>
+      </c>
+      <c r="J13" s="0">
+        <v>4342</v>
+      </c>
+      <c r="K13" s="0">
+        <v>9598.75</v>
+      </c>
+      <c r="L13" s="0">
+        <v>35.140000000000001</v>
+      </c>
+      <c r="M13" s="0">
+        <v>0.071999999999999995</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="0">
+        <v>11423099744</v>
+      </c>
+      <c r="C14" s="0">
+        <v>14513771403</v>
+      </c>
+      <c r="D14" s="0">
+        <v>1985468</v>
+      </c>
+      <c r="E14" s="0">
+        <v>310</v>
+      </c>
+      <c r="F14" s="0">
+        <v>9315</v>
+      </c>
+      <c r="G14" s="0">
+        <v>1.27</v>
+      </c>
+      <c r="H14" s="0">
+        <v>12.859999999999999</v>
+      </c>
+      <c r="I14" s="0">
+        <v>78.709999999999994</v>
+      </c>
+      <c r="J14" s="0">
+        <v>5027</v>
+      </c>
+      <c r="K14" s="0">
+        <v>11035.620000000001</v>
+      </c>
+      <c r="L14" s="0">
+        <v>35.600000000000001</v>
+      </c>
+      <c r="M14" s="0">
+        <v>0.070999999999999994</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="0">
+        <v>195786373663</v>
+      </c>
+      <c r="C15" s="0">
+        <v>237004283312</v>
+      </c>
+      <c r="D15" s="0">
+        <v>724341</v>
+      </c>
+      <c r="E15" s="0">
+        <v>165</v>
+      </c>
+      <c r="F15" s="0">
+        <v>1007799</v>
+      </c>
+      <c r="G15" s="0">
+        <v>3.0800000000000001</v>
+      </c>
+      <c r="H15" s="0">
+        <v>10.039999999999999</v>
+      </c>
+      <c r="I15" s="0">
+        <v>82.609999999999999</v>
+      </c>
+      <c r="J15" s="0">
+        <v>1282</v>
+      </c>
+      <c r="K15" s="0">
+        <v>4893.6099999999997</v>
+      </c>
+      <c r="L15" s="0">
+        <v>27.440000000000001</v>
+      </c>
+      <c r="M15" s="0">
+        <v>0.068000000000000005</v>
       </c>
     </row>
   </sheetData>
